--- a/data/proteomics/main_organelle_fraction_test.xlsx
+++ b/data/proteomics/main_organelle_fraction_test.xlsx
@@ -9335,829 +9335,829 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01803026804590827</v>
+        <v>0.01586881893817463</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01748292829436701</v>
+        <v>0.01539552314636037</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01829294154079333</v>
+        <v>0.01611350665458875</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0207489280075657</v>
+        <v>0.01850213455232834</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02162955843349083</v>
+        <v>0.01930748526206271</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0214389603827203</v>
+        <v>0.01913459158021098</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02328282735600697</v>
+        <v>0.02107283417852956</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02321255700441935</v>
+        <v>0.02092885425103025</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0236276051189767</v>
+        <v>0.02144079283369025</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03352035824047881</v>
+        <v>0.03120087039128269</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03525793441986056</v>
+        <v>0.03225925277724111</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0350053671367859</v>
+        <v>0.03214815266124662</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03357367285363724</v>
+        <v>0.03046475333633993</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03117969297055179</v>
+        <v>0.02900129521841597</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03093908228736083</v>
+        <v>0.02887423830555055</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03119288112981081</v>
+        <v>0.0290765389652627</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03655582241458174</v>
+        <v>0.03351270219208633</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03797469593825299</v>
+        <v>0.03488986093845756</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02996390383331973</v>
+        <v>0.0260269543998983</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03896523082205521</v>
+        <v>0.03538565938682151</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03864742844305991</v>
+        <v>0.03499463297624696</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04030153235511828</v>
+        <v>0.03660020709395863</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03984655307410836</v>
+        <v>0.03654546983156581</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03817711417600041</v>
+        <v>0.03488545927546538</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04023259234875153</v>
+        <v>0.03702034027690556</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.03313005511437598</v>
+        <v>0.03014302822959092</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0334749828132796</v>
+        <v>0.03058543816981969</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.03324864686176451</v>
+        <v>0.03061345582066066</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.02926070816775622</v>
+        <v>0.02654201983267612</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02996509124416948</v>
+        <v>0.02728960737867644</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0311339489499342</v>
+        <v>0.02838695952601056</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.02959994877518263</v>
+        <v>0.02794303462884194</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.03104650339433907</v>
+        <v>0.02931021512868822</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02861529161772577</v>
+        <v>0.02651096165186423</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02964068193499075</v>
+        <v>0.02754403918861262</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03091571439600326</v>
+        <v>0.02837829424692885</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0303917397216248</v>
+        <v>0.02772499274720956</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.04072031190800449</v>
+        <v>0.03678563641826819</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0386034686203368</v>
+        <v>0.03490871951553973</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.03903160295556057</v>
+        <v>0.03580260633577586</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.03126299935187809</v>
+        <v>0.02908780644374187</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.02968292590180479</v>
+        <v>0.02750452033421734</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.02996881582267782</v>
+        <v>0.02765710192656097</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.03982219412090837</v>
+        <v>0.03668939118616868</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.04017166104771553</v>
+        <v>0.03676769226606511</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.04004050320528197</v>
+        <v>0.03706220473793451</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.03082934003629595</v>
+        <v>0.02863198931267543</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.03212123142611319</v>
+        <v>0.03002415643569439</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.03057936637962769</v>
+        <v>0.02795138483717533</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.03292787438438733</v>
+        <v>0.02967477797398849</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.03924253300921932</v>
+        <v>0.03620037306869815</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.03494878726680889</v>
+        <v>0.03197899333837728</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.03704291814259099</v>
+        <v>0.03116588567975099</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03159725593427185</v>
+        <v>0.02852544486617229</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.02839027698746015</v>
+        <v>0.0253418105726208</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.03727899639809906</v>
+        <v>0.03369260300274828</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.03713622096093502</v>
+        <v>0.03355293044981636</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.03096381331752697</v>
+        <v>0.02757809707093501</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.03173595099846697</v>
+        <v>0.02831677227673254</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.03203230990865141</v>
+        <v>0.02861268260098924</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.03324620150955885</v>
+        <v>0.02970017241874595</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.03612536515333082</v>
+        <v>0.03240142815051038</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03555244004303773</v>
+        <v>0.03183468390813927</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03220082541812505</v>
+        <v>0.02688524517115465</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.04328395613253005</v>
+        <v>0.03753671671803375</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0411964438323608</v>
+        <v>0.03582109920550925</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04346507753415321</v>
+        <v>0.0374544056774378</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.02575244529220699</v>
+        <v>0.02125186101577688</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02540616048901005</v>
+        <v>0.02083273415838184</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.02671928048672387</v>
+        <v>0.02234836726722722</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.02911066126072585</v>
+        <v>0.02470192503460165</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.04998549798779832</v>
+        <v>0.043349085418838</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.05160472704748951</v>
+        <v>0.04469708347533861</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.04637797001575004</v>
+        <v>0.03914652684756483</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.05372173776069399</v>
+        <v>0.04468085078741804</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.04760658788975286</v>
+        <v>0.04120070757521523</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.04919622199178473</v>
+        <v>0.0426336553920634</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.04472591898345868</v>
+        <v>0.03825486956005882</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.04562475714255253</v>
+        <v>0.03912555906992792</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.04915065376741418</v>
+        <v>0.04205481655317424</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.05253645193727348</v>
+        <v>0.04516541248592287</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.03949681136355471</v>
+        <v>0.03506398638351289</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.04321380530927146</v>
+        <v>0.03950987020699947</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.04320063197741959</v>
+        <v>0.03919290071589095</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0411594188226288</v>
+        <v>0.03701809246967271</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.04062240919884246</v>
+        <v>0.03638365645764761</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.04188924295594923</v>
+        <v>0.0381133298950167</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.03590075898064255</v>
+        <v>0.03179675548004913</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.04342618906800075</v>
+        <v>0.03953491516833405</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.04616364938801048</v>
+        <v>0.04217989068650081</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.06875383983744196</v>
+        <v>0.0650224037802643</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.07105804735989782</v>
+        <v>0.06719002477909593</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0332064974023778</v>
+        <v>0.02749600004359149</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.03230881858420291</v>
+        <v>0.02650767503346731</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.03225716495490028</v>
+        <v>0.02645580700447475</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.03376295193927906</v>
+        <v>0.02849346659461099</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.03319062510147334</v>
+        <v>0.02796782330493172</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.03311729257701201</v>
+        <v>0.02803947187313833</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.03629375250054764</v>
+        <v>0.03147338640856966</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.03640030381544079</v>
+        <v>0.03142561308821554</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.03620441751657769</v>
+        <v>0.03128221893844529</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.03462984057460296</v>
+        <v>0.02977845832327267</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03499983674073084</v>
+        <v>0.03011363204380263</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.03531970581146303</v>
+        <v>0.03051639124083637</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.03428947840042797</v>
+        <v>0.02938933015083066</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.03121255036852811</v>
+        <v>0.02658976976534639</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.03143773869771637</v>
+        <v>0.02667338107030038</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.02785898361109388</v>
+        <v>0.02339423091049549</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.02816382594811402</v>
+        <v>0.02375825907957917</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.02896082963442809</v>
+        <v>0.02443137860517351</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02690805189772134</v>
+        <v>0.02258716766451916</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02547172805960069</v>
+        <v>0.02128735715067308</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.02682105815018884</v>
+        <v>0.0224941295888395</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.02516323505064982</v>
+        <v>0.02071559002919215</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.02546184290817665</v>
+        <v>0.02117851506180641</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.02516127039909378</v>
+        <v>0.02078622778107097</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.02491275735936107</v>
+        <v>0.0205783626091841</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.02596303091698994</v>
+        <v>0.02147780182709025</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.02511812869481908</v>
+        <v>0.02057657472590282</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01695964103488313</v>
+        <v>0.01420982784246704</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01626117052160417</v>
+        <v>0.01355848995539344</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.01682086634580286</v>
+        <v>0.01402508445624701</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.01757467330675895</v>
+        <v>0.0148619471746447</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.01657076330908922</v>
+        <v>0.01383210147907006</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.01723108499181484</v>
+        <v>0.01450257040405065</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0165095001898946</v>
+        <v>0.01358319035938908</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01664991850213463</v>
+        <v>0.01371770853954028</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.01670270689251083</v>
+        <v>0.01364851656028972</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01756933816719333</v>
+        <v>0.01454024994318983</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01815686518548249</v>
+        <v>0.01507744516143908</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.01677066191279285</v>
+        <v>0.01373983367939589</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.01732293979453242</v>
+        <v>0.01430476256422019</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01718442133897904</v>
+        <v>0.01413688332089994</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.01683755574354388</v>
+        <v>0.01382952381643274</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.01706674240805416</v>
+        <v>0.01406630245734811</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01659106431397621</v>
+        <v>0.01357327573156591</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0174352468664832</v>
+        <v>0.01439500978212316</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01641255435808567</v>
+        <v>0.01362520649001525</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01623044906175327</v>
+        <v>0.01347084905038523</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0161209279363941</v>
+        <v>0.01343357603322877</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.01596984728969496</v>
+        <v>0.01324353613772396</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01595520487137955</v>
+        <v>0.01320863678349187</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.01573377037735662</v>
+        <v>0.01305308838114149</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01695327803524116</v>
+        <v>0.0139584531719384</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01669779995578921</v>
+        <v>0.01365756926198127</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.01682814190709866</v>
+        <v>0.01363597436732387</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01642880779925259</v>
+        <v>0.01347303135242321</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01658335284660859</v>
+        <v>0.01358551738236597</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0164127821244763</v>
+        <v>0.01340440333495658</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.04204763563652</v>
+        <v>0.03989700266171447</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.04437904977256073</v>
+        <v>0.04206880443556749</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.04574778136116295</v>
+        <v>0.04237187505948973</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.05831343241183388</v>
+        <v>0.05486185633818676</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.05448440735515319</v>
+        <v>0.05190461890483825</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.05515164892521505</v>
+        <v>0.05218744612224083</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0559788157554891</v>
+        <v>0.05284443019643498</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.05689090490262664</v>
+        <v>0.05362303446660036</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.03475100444506776</v>
+        <v>0.03012364104368797</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.03286187557905203</v>
+        <v>0.02835299920418864</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.03240631862809663</v>
+        <v>0.02799995842394147</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.03285393095896647</v>
+        <v>0.02834576851347045</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0325682728616506</v>
+        <v>0.02818560136052427</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.03249829083347979</v>
+        <v>0.02805001789016354</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.02559377133230489</v>
+        <v>0.02174509707182248</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0261677327557271</v>
+        <v>0.02222459046383899</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02554319594276959</v>
+        <v>0.02193836283394224</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.02547775261152336</v>
+        <v>0.02185448797374463</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.03375571915703679</v>
+        <v>0.02859198518681476</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.03421974701302921</v>
+        <v>0.02898337722449479</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.03130480671676672</v>
+        <v>0.02662220021625486</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.03141751145208622</v>
+        <v>0.02690863849850235</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.02941409106050407</v>
+        <v>0.02516217636461664</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0301736484122932</v>
+        <v>0.02572723470931053</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0289999499126811</v>
+        <v>0.02506401143158745</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02960595009201453</v>
+        <v>0.02565189561394973</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.03767801522383278</v>
+        <v>0.03269138932655732</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.03742311242165922</v>
+        <v>0.03251429099668077</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.03718335284361413</v>
+        <v>0.03221075069681559</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.03719663520077934</v>
+        <v>0.0322100652681317</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.03297432119382909</v>
+        <v>0.02832782993031214</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.03058517906349323</v>
+        <v>0.02608135119605624</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.02906266385816022</v>
+        <v>0.02459323460276712</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.02944474303541524</v>
+        <v>0.02495465582880202</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.02940669996894018</v>
+        <v>0.02491339050681727</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.02840955405448353</v>
+        <v>0.0238954391201045</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.02821542623791547</v>
+        <v>0.02378388334176812</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.02817007228429229</v>
+        <v>0.02376303617847992</v>
       </c>
       <c r="GH11" t="n">
-        <v>0.02847310843088738</v>
+        <v>0.02403822511771844</v>
       </c>
       <c r="GI11" t="n">
-        <v>0.02807790676549595</v>
+        <v>0.02372934525306625</v>
       </c>
       <c r="GJ11" t="n">
-        <v>0.04014601105235222</v>
+        <v>0.03576463139682843</v>
       </c>
       <c r="GK11" t="n">
-        <v>0.03226187156839502</v>
+        <v>0.0284756204363586</v>
       </c>
       <c r="GL11" t="n">
-        <v>0.03620259253669342</v>
+        <v>0.03203481896995206</v>
       </c>
       <c r="GM11" t="n">
-        <v>0.03548991407736184</v>
+        <v>0.03107352647633831</v>
       </c>
       <c r="GN11" t="n">
-        <v>0.03279158723772792</v>
+        <v>0.02847633188384448</v>
       </c>
       <c r="GO11" t="n">
-        <v>0.04019564735324895</v>
+        <v>0.03548666894222219</v>
       </c>
       <c r="GP11" t="n">
-        <v>0.03885634264239862</v>
+        <v>0.03389231364221131</v>
       </c>
       <c r="GQ11" t="n">
-        <v>0.04134567462096527</v>
+        <v>0.03638768427073239</v>
       </c>
       <c r="GR11" t="n">
-        <v>0.03836614636262637</v>
+        <v>0.03344776566092374</v>
       </c>
       <c r="GS11" t="n">
-        <v>0.03968418052156585</v>
+        <v>0.034189673958566</v>
       </c>
       <c r="GT11" t="n">
-        <v>0.04114482105697716</v>
+        <v>0.03601682143884999</v>
       </c>
       <c r="GU11" t="n">
-        <v>0.04134902758425705</v>
+        <v>0.03586517352016064</v>
       </c>
       <c r="GV11" t="n">
-        <v>0.03851464346660409</v>
+        <v>0.03323963365659201</v>
       </c>
       <c r="GW11" t="n">
-        <v>0.03822219772180955</v>
+        <v>0.03392932372840948</v>
       </c>
       <c r="GX11" t="n">
-        <v>0.0357313877539856</v>
+        <v>0.03098280493673482</v>
       </c>
       <c r="GY11" t="n">
-        <v>0.03550953116800237</v>
+        <v>0.03070547129770306</v>
       </c>
       <c r="GZ11" t="n">
-        <v>0.03688300189976602</v>
+        <v>0.03228842296034557</v>
       </c>
       <c r="HA11" t="n">
-        <v>0.04214512086139264</v>
+        <v>0.03796147934228211</v>
       </c>
       <c r="HB11" t="n">
-        <v>0.03914441042222311</v>
+        <v>0.03495785721087763</v>
       </c>
       <c r="HC11" t="n">
-        <v>0.04260052438845484</v>
+        <v>0.03830718086178712</v>
       </c>
       <c r="HD11" t="n">
-        <v>0.03410537493925685</v>
+        <v>0.02971999292309587</v>
       </c>
       <c r="HE11" t="n">
-        <v>0.03769443758453687</v>
+        <v>0.03315240139216942</v>
       </c>
       <c r="HF11" t="n">
-        <v>0.05788282000160429</v>
+        <v>0.05400991490454313</v>
       </c>
       <c r="HG11" t="n">
-        <v>0.06428529428923181</v>
+        <v>0.05970655577794666</v>
       </c>
       <c r="HH11" t="n">
-        <v>0.01234325869500486</v>
+        <v>0.01094496212584717</v>
       </c>
       <c r="HI11" t="n">
-        <v>0.06348717250615883</v>
+        <v>0.05785724718659141</v>
       </c>
       <c r="HJ11" t="n">
-        <v>0.04157845566893709</v>
+        <v>0.03766679017293154</v>
       </c>
       <c r="HK11" t="n">
-        <v>0.01751447444778874</v>
+        <v>0.01599351886724453</v>
       </c>
       <c r="HL11" t="n">
-        <v>0.04998549798779832</v>
+        <v>0.043349085418838</v>
       </c>
       <c r="HM11" t="n">
-        <v>0.07911161488169936</v>
+        <v>0.07260861721956878</v>
       </c>
       <c r="HN11" t="n">
-        <v>0.08435413714943767</v>
+        <v>0.07620757679948661</v>
       </c>
       <c r="HO11" t="n">
-        <v>0.07247904725556896</v>
+        <v>0.06616113307749831</v>
       </c>
       <c r="HP11" t="n">
-        <v>0.07996177225143862</v>
+        <v>0.07406391168080947</v>
       </c>
       <c r="HQ11" t="n">
-        <v>0.07242892248958153</v>
+        <v>0.06614745010975547</v>
       </c>
       <c r="HR11" t="n">
-        <v>0.0744880663318678</v>
+        <v>0.068061038051107</v>
       </c>
       <c r="HS11" t="n">
-        <v>0.04654206661224328</v>
+        <v>0.04323538973331555</v>
       </c>
       <c r="HT11" t="n">
-        <v>0.04565440125141998</v>
+        <v>0.04308689323180567</v>
       </c>
       <c r="HU11" t="n">
-        <v>0.01099798653695148</v>
+        <v>0.01008466003769424</v>
       </c>
       <c r="HV11" t="n">
-        <v>0.09612446806532102</v>
+        <v>0.09074574750540208</v>
       </c>
       <c r="HW11" t="n">
-        <v>0.05625332602675107</v>
+        <v>0.0530867419604279</v>
       </c>
       <c r="HX11" t="n">
-        <v>0.2152993042919082</v>
+        <v>0.2029880582175483</v>
       </c>
       <c r="HY11" t="n">
-        <v>0.06748772784892458</v>
+        <v>0.06301263235724004</v>
       </c>
       <c r="HZ11" t="n">
-        <v>0.04548238908254406</v>
+        <v>0.04235712576445196</v>
       </c>
       <c r="IA11" t="n">
-        <v>0.03314074978143011</v>
+        <v>0.03135689131249945</v>
       </c>
       <c r="IB11" t="n">
-        <v>0.08401683992106432</v>
+        <v>0.07972861638130026</v>
       </c>
       <c r="IC11" t="n">
-        <v>0.04565440125141998</v>
+        <v>0.04308689323180567</v>
       </c>
       <c r="ID11" t="n">
-        <v>0.04412741951577035</v>
+        <v>0.04061437218501651</v>
       </c>
       <c r="IE11" t="n">
-        <v>0.0347750794233533</v>
+        <v>0.03357234421265363</v>
       </c>
       <c r="IF11" t="n">
-        <v>0.04375489997755289</v>
+        <v>0.04218549769027121</v>
       </c>
       <c r="IG11" t="n">
-        <v>0.05625332602675107</v>
+        <v>0.0530867419604279</v>
       </c>
       <c r="IH11" t="n">
-        <v>0.05275557984447701</v>
+        <v>0.0490214770883347</v>
       </c>
       <c r="II11" t="n">
-        <v>0.07854610883552603</v>
+        <v>0.07461741373751432</v>
       </c>
       <c r="IJ11" t="n">
-        <v>0.03314074978143011</v>
+        <v>0.03135689131249945</v>
       </c>
       <c r="IK11" t="n">
-        <v>0.04890017505075725</v>
+        <v>0.04558751491662098</v>
       </c>
       <c r="IL11" t="n">
-        <v>0.01241930293838614</v>
+        <v>0.01154722221963509</v>
       </c>
       <c r="IM11" t="n">
-        <v>0.01308128265604421</v>
+        <v>0.01199158176955625</v>
       </c>
       <c r="IN11" t="n">
-        <v>0.04548238908254406</v>
+        <v>0.04235712576445196</v>
       </c>
       <c r="IO11" t="n">
-        <v>0.04698438602584671</v>
+        <v>0.0427374061895589</v>
       </c>
       <c r="IP11" t="n">
-        <v>0.03971455856546428</v>
+        <v>0.03725366396541416</v>
       </c>
       <c r="IQ11" t="n">
-        <v>0.02909761221528902</v>
+        <v>0.02668509164313289</v>
       </c>
       <c r="IR11" t="n">
-        <v>0.04654206661224328</v>
+        <v>0.04323538973331555</v>
       </c>
       <c r="IS11" t="n">
-        <v>0.04655238845200497</v>
+        <v>0.04310110447114081</v>
       </c>
       <c r="IT11" t="n">
-        <v>0.04611910408727013</v>
+        <v>0.04212180383635666</v>
       </c>
       <c r="IU11" t="n">
-        <v>0.08351029196032118</v>
+        <v>0.0792500738966741</v>
       </c>
       <c r="IV11" t="n">
-        <v>0.04157778680508444</v>
+        <v>0.03766618436994543</v>
       </c>
       <c r="IW11" t="n">
-        <v>0.03806029067161544</v>
+        <v>0.03416002706670198</v>
       </c>
       <c r="IX11" t="n">
-        <v>0.03323736264881975</v>
+        <v>0.02952449150976564</v>
       </c>
       <c r="IY11" t="n">
-        <v>0.0351436497321553</v>
+        <v>0.03134851719926444</v>
       </c>
       <c r="IZ11" t="n">
-        <v>0.02518586278852001</v>
+        <v>0.02218283738260101</v>
       </c>
       <c r="JA11" t="n">
-        <v>0.0270677260841751</v>
+        <v>0.02408304880145698</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.02675845405052958</v>
+        <v>0.02364838968914399</v>
       </c>
       <c r="JC11" t="n">
-        <v>0.032699860226448</v>
+        <v>0.02916547100758868</v>
       </c>
       <c r="JD11" t="n">
-        <v>0.04072253903395624</v>
+        <v>0.03659846696941243</v>
       </c>
       <c r="JE11" t="n">
-        <v>0.03751438590808252</v>
+        <v>0.03351688498777873</v>
       </c>
       <c r="JF11" t="n">
-        <v>0.03707139972912243</v>
+        <v>0.03309327200420761</v>
       </c>
       <c r="JG11" t="n">
-        <v>0.04303775999081296</v>
+        <v>0.03885371992524111</v>
       </c>
       <c r="JH11" t="n">
-        <v>0.03922886021569393</v>
+        <v>0.03539776462723459</v>
       </c>
       <c r="JI11" t="n">
-        <v>0.04052728588111298</v>
+        <v>0.03656327514608591</v>
       </c>
       <c r="JJ11" t="n">
-        <v>0.03984831358479993</v>
+        <v>0.03592043812148756</v>
       </c>
       <c r="JK11" t="n">
-        <v>0.03815508898438087</v>
+        <v>0.03431591380200812</v>
       </c>
       <c r="JL11" t="n">
-        <v>0.03966507716474259</v>
+        <v>0.03580265057187022</v>
       </c>
       <c r="JM11" t="n">
-        <v>0.0394018271338614</v>
+        <v>0.03559422603211682</v>
       </c>
       <c r="JN11" t="n">
-        <v>0.04415399859784971</v>
+        <v>0.03990923679714038</v>
       </c>
       <c r="JO11" t="n">
-        <v>0.03753866976848746</v>
+        <v>0.03396589411908573</v>
       </c>
       <c r="JP11" t="n">
-        <v>0.04386303456024704</v>
+        <v>0.03967860873191348</v>
       </c>
       <c r="JQ11" t="n">
-        <v>0.03844828914873333</v>
+        <v>0.03456603004743604</v>
       </c>
     </row>
     <row r="12">
